--- a/assets/haulz-td-templates/proforma.xlsx
+++ b/assets/haulz-td-templates/proforma.xlsx
@@ -31,10 +31,10 @@
     <t xml:space="preserve">10229010/280426/                /     </t>
   </si>
   <si>
-    <t>ГРУЗОТПРАВИТЕЛЬ: ООО"ХОЛЗ"  Россия, г. Калининград  склада железнодорожная 12 склад 23</t>
-  </si>
-  <si>
-    <t>ГРУЗОПОЛУЧАТЕЛЬ: ООО"ХОЛЗ" Россия, г. Москва, 117997, ул. Вавилова, д. 19</t>
+    <t>ГРУЗООТПРАВИТЕЛЬ: ООО «ХОЛЗ»  Россия, г. Калининград, ул. Железнодорожная 12 склад 23</t>
+  </si>
+  <si>
+    <t>ГРУЗОПОЛУЧАТЕЛЬ: ООО «ХОЛЗ» Россия, г. Москва, ул. Вавилова, д. 19</t>
   </si>
   <si>
     <t>№ П/П</t>
@@ -82869,6 +82869,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>